--- a/data/current/Status_Eng_Proc_Cons.xlsx
+++ b/data/current/Status_Eng_Proc_Cons.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Polonia\MONTHLY REPORT\Monthly report\REPORT 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WTE\WTE_option118 - public Github Page\List of documents need to updated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C07384-0C40-45AF-913B-99AE5224968B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5C588D-8819-444F-B69B-F9E8CCA96B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng_Proc_Cons" sheetId="1" r:id="rId1"/>
@@ -151,13 +151,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -458,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="40.1328125" customWidth="1"/>
@@ -466,78 +465,64 @@
     <col min="3" max="3" width="24.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7">
-        <v>0.41</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0.41</v>
+      <c r="B2" s="6">
+        <v>0.54</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="C3" s="9">
-        <v>0.06</v>
+      <c r="B3" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.09</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8">
-        <v>0.02</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.02</v>
+      <c r="B4" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.03</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>0</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B6" s="1"/>
+      <c r="C6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/current/Status_Eng_Proc_Cons.xlsx
+++ b/data/current/Status_Eng_Proc_Cons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WTE\WTE_option118 - public Github Page\List of documents need to updated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WTE\WTE_option142 - public Github Page + password\wte-dashboard-v127-qr-absolute-url-fix\wte-dashboard-v127-qr-absolute-url-fix\data\current\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5C588D-8819-444F-B69B-F9E8CCA96B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74B6933-5C0C-4A56-B935-9903AFFCB993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng_Proc_Cons" sheetId="1" r:id="rId1"/>
@@ -481,10 +481,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="6">
-        <v>0.54</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="C2" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -492,10 +492,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="7">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="C3" s="8">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -503,10 +503,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="7">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11</v>
       </c>
       <c r="C4" s="8">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
